--- a/data/mini-example-resilience/Power_WeightsRP.xlsx
+++ b/data/mini-example-resilience/Power_WeightsRP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E4DC38-6A8B-4216-B46D-FFF11A6DE73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90148D15-EFB6-4ED1-963F-1CEDDBD25B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,7 +735,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="12">
-        <v>365</v>
+        <v>1</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>26</v>
